--- a/results/greedy/UAVs6_GRID13/tour/UAVs6_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs6_GRID13/tour/UAVs6_GRID13_1920_16_Greedy_sequences.xlsx
@@ -592,7 +592,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02804629202000797</v>
+        <v>0.0275510840001516</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03690004203235731</v>
+        <v>0.029060082975775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03263229102594778</v>
+        <v>0.02896591601893306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02573637501336634</v>
+        <v>0.02519029099494219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0312337499926798</v>
+        <v>0.02998950000619516</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03071870899293572</v>
+        <v>0.03044012497412041</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03055279195541516</v>
+        <v>0.02990545897046104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02748987497761846</v>
+        <v>0.02715791697846726</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03035270801046863</v>
+        <v>0.02997070801211521</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03298349998658523</v>
+        <v>0.0320966670406051</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02276308299042284</v>
+        <v>0.02213308302452788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03000529197743163</v>
+        <v>0.02938554203137755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02495524997357279</v>
+        <v>0.02459899999666959</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02932979201432317</v>
+        <v>0.02867737499764189</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02864808298181742</v>
+        <v>0.02806012501241639</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03186549997190014</v>
+        <v>0.03133200004231185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02667979203397408</v>
+        <v>0.02627416700124741</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02577841700986028</v>
+        <v>0.02515916700940579</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02623550000134856</v>
+        <v>0.02558374998625368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02418829197995365</v>
+        <v>0.02388908399734646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02640483301365748</v>
+        <v>0.02579054201487452</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02762520901160315</v>
+        <v>0.02694612502818927</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02939370804233477</v>
+        <v>0.02840050001395866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02317825000500306</v>
+        <v>0.02285841701086611</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0234663329902105</v>
+        <v>0.02288550004595891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02456766698742285</v>
+        <v>0.0240295419935137</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02583108399994671</v>
+        <v>0.02483004203531891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02447958296397701</v>
+        <v>0.02422020799713209</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02587533398764208</v>
+        <v>0.02501554199261591</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02292324998416007</v>
+        <v>0.02251079102279618</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03072666696971282</v>
+        <v>0.02998737496091053</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0286375829600729</v>
+        <v>0.02770108298864216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02811579097760841</v>
+        <v>0.02731404203223065</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02057129103923216</v>
+        <v>0.01968445797683671</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02303250000113621</v>
+        <v>0.02241412497824058</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02562670799670741</v>
+        <v>0.02500183403026313</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02507537498604506</v>
+        <v>0.02460491703823209</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03573325002798811</v>
+        <v>0.03423070901772007</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02825245802523568</v>
+        <v>0.0272982909809798</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02291500003775582</v>
+        <v>0.02249549998668954</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02236175001598895</v>
+        <v>0.02186662500025705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02779337496031076</v>
+        <v>0.02725995797663927</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02225549996364862</v>
+        <v>0.02183670795056969</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03289349999977276</v>
+        <v>0.03245666698785499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02922941703582183</v>
+        <v>0.02913016703678295</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03006787499180064</v>
+        <v>0.0291592919966206</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02757241699146107</v>
+        <v>0.02697312500094995</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0240195409860462</v>
+        <v>0.02330291602993384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03523837501415983</v>
+        <v>0.03440866596065462</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02294999995501712</v>
+        <v>0.0221745420130901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02549579204060137</v>
+        <v>0.02480949996970594</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03239870897959918</v>
+        <v>0.03213399997912347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02118820796022192</v>
+        <v>0.02047841699095443</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03296862496063113</v>
+        <v>0.03150616702623665</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02273354097269475</v>
+        <v>0.02212233399040997</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0223595830029808</v>
+        <v>0.02182029199320823</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02914420899469405</v>
+        <v>0.02853287500329316</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02761366701452062</v>
+        <v>0.0265000420040451</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02441933302907273</v>
+        <v>0.02401812502648681</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02959287498379126</v>
+        <v>0.02911466598743573</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02671712497249246</v>
+        <v>0.02613087499048561</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0225529579911381</v>
+        <v>0.02203629101859406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02911645901622251</v>
+        <v>0.02797604200895876</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02635658299550414</v>
+        <v>0.02559224999276921</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02832637500250712</v>
+        <v>0.02802262495970353</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.018693916965276</v>
+        <v>0.01814066700171679</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02856537501793355</v>
+        <v>0.02750108402688056</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02650487498613074</v>
+        <v>0.02598204195965081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03212895803153515</v>
+        <v>0.03146958304569125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03386441600741819</v>
+        <v>0.03326870797900483</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03095495799789205</v>
+        <v>0.03029316599713638</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03382212499855086</v>
+        <v>0.03341795899905264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02628645900404081</v>
+        <v>0.02540375001262873</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02387029200326651</v>
+        <v>0.02334874996449798</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01989799999864772</v>
+        <v>0.01926079200347885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02778295904863626</v>
+        <v>0.02705150004476309</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02431704197078943</v>
+        <v>0.02372220804682001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02818900003330782</v>
+        <v>0.04063112504081801</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02522391697857529</v>
+        <v>0.0246574169723317</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02978179103229195</v>
+        <v>0.03028616699157283</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02558195899473503</v>
+        <v>0.02662887499900535</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02285150001989678</v>
+        <v>0.02309679199242964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02613937499700114</v>
+        <v>0.02579512499505654</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02270054101245478</v>
+        <v>0.02397270803339779</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02567474998068064</v>
+        <v>0.02504316699923947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0215961670037359</v>
+        <v>0.02129658398916945</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02781754202442244</v>
+        <v>0.02801612502662465</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03214366600150242</v>
+        <v>0.03372850001323968</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0320017909980379</v>
+        <v>0.03101445798529312</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0298285839962773</v>
+        <v>0.02932083298219368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03138875000877306</v>
+        <v>0.03034300002036616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03208912501577288</v>
+        <v>0.03282512497389689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03009299997938797</v>
+        <v>0.02883758302778006</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02531758398981765</v>
+        <v>0.02508187503553927</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03277570899808779</v>
+        <v>0.034128499974031</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02131770900450647</v>
+        <v>0.02054620900889859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02717120799934492</v>
+        <v>0.02560979197733104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02273395896190777</v>
+        <v>0.02163216704502702</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02966895798454061</v>
+        <v>0.02926754101645201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02774366701487452</v>
+        <v>0.02726070798235014</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/results/greedy/UAVs6_GRID13/tour/UAVs6_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs6_GRID13/tour/UAVs6_GRID13_1920_16_Greedy_sequences.xlsx
@@ -592,7 +592,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0275510840001516</v>
+        <v>0.02755733398953453</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.029060082975775</v>
+        <v>0.02828637498896569</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02896591601893306</v>
+        <v>0.02869045798433945</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02519029099494219</v>
+        <v>0.02499345800606534</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02998950000619516</v>
+        <v>0.02973050001310185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03044012497412041</v>
+        <v>0.02997870795661584</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02990545897046104</v>
+        <v>0.02993004204472527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02715791697846726</v>
+        <v>0.02708804199937731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02997070801211521</v>
+        <v>0.02979695901740342</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0320966670406051</v>
+        <v>0.03204587497748435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02213308302452788</v>
+        <v>0.02203879103763029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02938554203137755</v>
+        <v>0.02924466598778963</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02459899999666959</v>
+        <v>0.024542500032112</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02867737499764189</v>
+        <v>0.02895883400924504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02806012501241639</v>
+        <v>0.027952250035014</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03133200004231185</v>
+        <v>0.03117195802042261</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02627416700124741</v>
+        <v>0.02581083303084597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02515916700940579</v>
+        <v>0.02495608403114602</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02558374998625368</v>
+        <v>0.02532866696128622</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02388908399734646</v>
+        <v>0.02378091699210927</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02579054201487452</v>
+        <v>0.02578399999765679</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02694612502818927</v>
+        <v>0.02715745801106095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02840050001395866</v>
+        <v>0.02872529096202925</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02285841701086611</v>
+        <v>0.02205320802750066</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02288550004595891</v>
+        <v>0.0226876669912599</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0240295419935137</v>
+        <v>0.02407508401665837</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02483004203531891</v>
+        <v>0.02479741699062288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02422020799713209</v>
+        <v>0.02385004103416577</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02501554199261591</v>
+        <v>0.02524904196616262</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02251079102279618</v>
+        <v>0.02236854197690263</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02998737496091053</v>
+        <v>0.02994375000707805</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02770108298864216</v>
+        <v>0.02828812500229105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02731404203223065</v>
+        <v>0.02752545895054936</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01968445797683671</v>
+        <v>0.01977750001242384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02241412497824058</v>
+        <v>0.02261337504023686</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02500183403026313</v>
+        <v>0.02485266700387001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02460491703823209</v>
+        <v>0.02436800004215911</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03423070901772007</v>
+        <v>0.03459945798385888</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0272982909809798</v>
+        <v>0.02705958299338818</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02249549998668954</v>
+        <v>0.02210050000576302</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02186662500025705</v>
+        <v>0.02191974996821955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02725995797663927</v>
+        <v>0.02767891599796712</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02183670795056969</v>
+        <v>0.02188141603255644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03245666698785499</v>
+        <v>0.03229979198658839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02913016703678295</v>
+        <v>0.02872475003823638</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0291592919966206</v>
+        <v>0.02910008298931643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02697312500094995</v>
+        <v>0.02669141598744318</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02330291602993384</v>
+        <v>0.02336712501710281</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03440866596065462</v>
+        <v>0.03441462496994063</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0221745420130901</v>
+        <v>0.02217466704314575</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02480949996970594</v>
+        <v>0.02473520900821313</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03213399997912347</v>
+        <v>0.03165950003312901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02047841699095443</v>
+        <v>0.02059241698589176</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03150616702623665</v>
+        <v>0.03202633402543142</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02212233399040997</v>
+        <v>0.02224858297267929</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02182029199320823</v>
+        <v>0.02185983402887359</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02853287500329316</v>
+        <v>0.02861116698477417</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0265000420040451</v>
+        <v>0.02665133395930752</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02401812502648681</v>
+        <v>0.02375087502878159</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02911466598743573</v>
+        <v>0.02924829197581857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02613087499048561</v>
+        <v>0.02636399999028072</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02203629101859406</v>
+        <v>0.02229129202896729</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02797604200895876</v>
+        <v>0.02816625003470108</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02559224999276921</v>
+        <v>0.02592591696884483</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02802262495970353</v>
+        <v>0.02770224999403581</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01814066700171679</v>
+        <v>0.01817208295688033</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02750108402688056</v>
+        <v>0.02831200003856793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02598204195965081</v>
+        <v>0.02540887502254918</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03146958304569125</v>
+        <v>0.03103662497596815</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03326870797900483</v>
+        <v>0.03305841697147116</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03029316599713638</v>
+        <v>0.03031791601097211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03341795899905264</v>
+        <v>0.03365245898021385</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02540375001262873</v>
+        <v>0.025476458016783</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02334874996449798</v>
+        <v>0.02364291698904708</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01926079200347885</v>
+        <v>0.01921608304837719</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02705150004476309</v>
+        <v>0.0271868749987334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02372220804682001</v>
+        <v>0.02378791698720306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04063112504081801</v>
+        <v>0.02726729097776115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0246574169723317</v>
+        <v>0.02448241703677922</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03028616699157283</v>
+        <v>0.02945349999936298</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02662887499900535</v>
+        <v>0.02479633403709158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02309679199242964</v>
+        <v>0.02232083299895748</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02579512499505654</v>
+        <v>0.02587308298097923</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02397270803339779</v>
+        <v>0.02228779101278633</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02504316699923947</v>
+        <v>0.0251517909928225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02129658398916945</v>
+        <v>0.02097833302104846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02801612502662465</v>
+        <v>0.02748600003542379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03372850001323968</v>
+        <v>0.03177649999270216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03101445798529312</v>
+        <v>0.03078141703736037</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02932083298219368</v>
+        <v>0.02893754199612886</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03034300002036616</v>
+        <v>0.03007224999601021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03282512497389689</v>
+        <v>0.03178312495583668</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02883758302778006</v>
+        <v>0.02954279200639576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02508187503553927</v>
+        <v>0.02561250003054738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.034128499974031</v>
+        <v>0.03307758399751037</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02054620900889859</v>
+        <v>0.02023070800350979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02560979197733104</v>
+        <v>0.02550645801238716</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02163216704502702</v>
+        <v>0.02126108400989324</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02926754101645201</v>
+        <v>0.0285469579976052</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02726070798235014</v>
+        <v>0.02685833297437057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
